--- a/results/Int Task Remove ACC -0.0/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.0/Linea_fi_all.xlsx
@@ -911,72 +911,72 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>-0.00048627995831882485 +/- 0.0008536440241364493</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.054602292462660705 +/- 0.0034762059057163786</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0443209447724905 +/- 0.003339552717394094</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0443209447724905 +/- 0.003339552717394094</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.02622438346648146 +/- 0.0015553048403777797</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.07078846821813134 +/- 0.0028124046516147467</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.04300104202848215 +/- 0.0017697449396119503</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>-0.011427579020493173 +/- 0.004577683292886957</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.00437651962486979 +/- 0.0035017945567567916</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.03327544286210495 +/- 0.0028802240280136025</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.26262591177492195 +/- 0.007684758908084753</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.023619312261201852 +/- 0.003549021125236482</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.08766932962834321 +/- 0.0077157031618838865</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>-0.0005557485237929538 +/- 0.0009084193699633076</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.054602292462660705 +/- 0.0034762059057163786</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0443209447724905 +/- 0.003339552717394094</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.0443209447724905 +/- 0.003339552717394094</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.02622438346648146 +/- 0.0015553048403777797</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.07078846821813134 +/- 0.0028124046516147467</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.04303577631121922 +/- 0.0017809577969148047</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.011427579020493173 +/- 0.004577683292886957</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.00437651962486979 +/- 0.0035017945567567916</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.03327544286210495 +/- 0.0028802240280136025</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.26262591177492195 +/- 0.007684758908084753</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.023619312261201852 +/- 0.003549021125236482</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.08766932962834321 +/- 0.0077157031618838865</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-0.00048627995831882485 +/- 0.0008536440241364493</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.03292810003473431 +/- 0.003074719829986908</t>
+          <t>0.032893365751997236 +/- 0.003083535827713268</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.21903114186851208 +/- 0.005979254773783496</t>
+          <t>0.21906574394463663 +/- 0.005939978275550318</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.03495212038303699 +/- 0.006827622278231352</t>
+          <t>0.0348837209302326 +/- 0.006841655053063007</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.0006030150753769004 +/- 0.0008314689210044344</t>
+          <t>-0.0006365159128978393 +/- 0.0007991196275964408</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.004824120603015047 +/- 0.002642959185703991</t>
+          <t>0.0047906197654941085 +/- 0.002638071306212402</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.047903225806451656 +/- 0.006843349004568962</t>
+          <t>0.04783870967741939 +/- 0.00678501439905777</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.011096774193548454 +/- 0.0017621290688706731</t>
+          <t>0.011129032258064575 +/- 0.0017386468358983173</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.0008562918838421751 +/- 0.0011298578485103242</t>
+          <t>-0.0008935219657483562 +/- 0.0011316965118072075</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.0018987341772152334 +/- 0.0017016224694008076</t>
+          <t>-0.0019359642591214143 +/- 0.001712583767684287</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.019303797468354443 +/- 0.0023188097178337133</t>
+          <t>0.01933895921237694 +/- 0.0023429439168716998</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.0013009845288326604 +/- 0.0006680731364275611</t>
+          <t>0.0012658227848101554 +/- 0.0005925562428393987</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03924135615978517 +/- 0.005329755739133612</t>
+          <t>0.0392749244712991 +/- 0.005398135193749615</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.004397448808324944 +/- 0.0019192738984790652</t>
+          <t>-0.004363880496811012 +/- 0.0018870049442840185</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.1649546827794562 +/- 0.006353551212794075</t>
+          <t>0.16492111446794228 +/- 0.006356831426150864</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.004363880496811012 +/- 0.0028641462245990756</t>
+          <t>0.004397448808324944 +/- 0.0029088447909889244</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.00134273246055725 +/- 0.000862385537339043</t>
+          <t>0.001309164149043318 +/- 0.0008146801678087627</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.0007508978126020249 +/- 0.001150108713928081</t>
+          <t>-0.0007835455435847294 +/- 0.0011422040930157296</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
